--- a/results_ablation/FP2_task3_ablation_result.xlsx
+++ b/results_ablation/FP2_task3_ablation_result.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="FP2_Task3_R1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="FP2_Task3_R2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FP2_Task3_Avg" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FP2_Task3_Avg" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,18 +449,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,42 +469,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ablation(BL+PG+Rec) 평균 GCR (%)</t>
+          <t>Baseline GCR (%)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Baseline 평균 GCR (%)</t>
+          <t>Ablation GCR (%)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>차이</t>
+          <t>Physical Guard GCR (%)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>개선율 (%)</t>
+          <t>Baseline Exec (%)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ablation 평균 Exec (%)</t>
+          <t>Ablation Exec (%)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Baseline 평균 Exec (%)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>차이 Exec</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>개선율 Exec (%)</t>
+          <t>Physical Guard Exec (%)</t>
         </is>
       </c>
     </row>
@@ -518,28 +505,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="H2" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17.08</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -549,28 +530,22 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>100</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>17.08</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -588,12 +563,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -604,32 +579,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ablation(BL+PG+Rec) GCR (%)</t>
+          <t>Baseline GCR (%)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Baseline GCR (%)</t>
+          <t>Ablation GCR (%)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>차이</t>
+          <t>Physical Guard GCR (%)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Ablation Exec (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Baseline Exec (%)</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>차이 Exec</t>
+          <t>Physical Guard Exec (%)</t>
         </is>
       </c>
     </row>
@@ -640,22 +615,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="F2" t="n">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>16.67</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -689,32 +664,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ablation(BL+PG+Rec) GCR (%)</t>
+          <t>Baseline 평균 GCR (%)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Baseline GCR (%)</t>
+          <t>Ablation 평균 GCR (%)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>차이</t>
+          <t>Physical Guard 평균 GCR (%)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ablation Exec (%)</t>
+          <t>Baseline 평균 Exec (%)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Baseline Exec (%)</t>
+          <t>Ablation 평균 Exec (%)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>차이 Exec</t>
+          <t>Physical Guard 평균 Exec (%)</t>
         </is>
       </c>
     </row>
@@ -725,151 +700,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="F2" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>12.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ablation 평균 GCR (%)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Baseline 평균 GCR (%)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>차이</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Ablation GCR (10회)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Baseline GCR (10회)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ablation 평균 Exec (%)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Baseline 평균 Exec (%)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>차이 Exec</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Ablation Exec (10회)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Baseline Exec (10회)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Put Pot on the StoveBurner and Put Mug in the Microwave</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>100.0, 100.0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>50.0, 50.0</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H2" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>100.0, 100.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>83.3, 87.5</t>
-        </is>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -879,27 +725,23 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
